--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -9851,10 +9851,10 @@
         <v>0.689874</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -10327,7 +10327,7 @@
         <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -10542,7 +10542,7 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J235" t="n">
         <v>1</v>
@@ -11442,10 +11442,10 @@
         <v>0.567971</v>
       </c>
       <c r="H256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J256" t="n">
         <v>1</v>
@@ -11786,10 +11786,10 @@
         <v>0.889556</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="I299" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J299" t="n">
         <v>1</v>
@@ -13509,7 +13509,7 @@
         <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>1</v>
+        <v>0.666667</v>
       </c>
       <c r="J304" t="n">
         <v>1</v>
@@ -13592,10 +13592,10 @@
         <v>0.345336</v>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I306" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J306" t="n">
         <v>1</v>
@@ -13721,10 +13721,10 @@
         <v>0.821087</v>
       </c>
       <c r="H309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J309" t="n">
         <v>1</v>
@@ -14068,7 +14068,7 @@
         <v>0</v>
       </c>
       <c r="I317" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -14584,7 +14584,7 @@
         <v>0</v>
       </c>
       <c r="I329" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J329" t="n">
         <v>0</v>
@@ -15143,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J342" t="n">
         <v>0</v>
@@ -15229,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="I344" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J344" t="n">
         <v>0</v>
@@ -15358,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J347" t="n">
         <v>0</v>
@@ -15831,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J358" t="n">
         <v>1</v>
@@ -16774,10 +16774,10 @@
         <v>0.425258</v>
       </c>
       <c r="H380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I380" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J380" t="n">
         <v>1</v>
@@ -16820,7 +16820,7 @@
         <v>0</v>
       </c>
       <c r="I381" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J381" t="n">
         <v>1</v>
@@ -16860,10 +16860,10 @@
         <v>0.392766</v>
       </c>
       <c r="H382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I382" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J382" t="n">
         <v>1</v>
@@ -17333,10 +17333,10 @@
         <v>0.651366</v>
       </c>
       <c r="H393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I393" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J393" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.447532</v>
+        <v>0.285729</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.205072</v>
+        <v>0.157905</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.251472</v>
+        <v>0.258879</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.973002</v>
+        <v>0.969388</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.271298</v>
+        <v>0.289025</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.5682120000000001</v>
+        <v>0.515524</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.116131</v>
+        <v>0.07646</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.090443</v>
+        <v>0.102231</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.178912</v>
+        <v>0.20528</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.127228</v>
+        <v>0.158497</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.422375</v>
+        <v>0.374448</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5416,10 +5416,10 @@
         <v>0.051415</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.562238</v>
+        <v>0.46681</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.396499</v>
+        <v>0.397211</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.259262</v>
+        <v>0.233245</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.642509</v>
+        <v>0.525992</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.265267</v>
+        <v>0.309484</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.257827</v>
+        <v>0.2865</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.681114</v>
+        <v>0.619625</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.619967</v>
+        <v>0.584145</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.281214</v>
+        <v>0.193484</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5803,10 +5803,10 @@
         <v>0.000682</v>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.518485</v>
+        <v>0.409657</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.381911</v>
+        <v>0.375635</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.340816</v>
+        <v>0.281943</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.208814</v>
+        <v>0.22675</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.766352</v>
+        <v>0.860638</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6018,10 +6018,10 @@
         <v>0.178138</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.420064</v>
+        <v>0.713438</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.181238</v>
+        <v>0.154271</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0.753749</v>
+        <v>0.696586</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.255126</v>
+        <v>0.378398</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.362663</v>
+        <v>0.329874</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.090998</v>
+        <v>0.074097</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.253899</v>
+        <v>0.215519</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.460974</v>
+        <v>0.418699</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2592</v>
+        <v>0.306975</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.337774</v>
+        <v>0.318961</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.195426</v>
+        <v>0.201099</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6491,10 +6491,10 @@
         <v>0.013948</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.617341</v>
+        <v>0.45025</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.448396</v>
+        <v>0.393142</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.377557</v>
+        <v>0.321188</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.475714</v>
+        <v>0.455847</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.144156</v>
+        <v>0.197117</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.333003</v>
+        <v>0.441291</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.331546</v>
+        <v>0.266126</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.182217</v>
+        <v>0.153379</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.304839</v>
+        <v>0.263294</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.161706</v>
+        <v>0.112119</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.502707</v>
+        <v>0.612778</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.9995309999999999</v>
+        <v>0.997577</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.158179</v>
+        <v>0.177526</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7050,10 +7050,10 @@
         <v>1e-06</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>0.453411</v>
+        <v>0.626099</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0.69503</v>
+        <v>0.594426</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.382818</v>
+        <v>0.419773</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.383284</v>
+        <v>0.326954</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.351823</v>
+        <v>0.364609</v>
       </c>
       <c r="H158" t="n">
         <v>1</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.261005</v>
+        <v>0.226784</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.252397</v>
+        <v>0.259068</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.346336</v>
+        <v>0.262689</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.208324</v>
+        <v>0.209056</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.877067</v>
+        <v>0.663453</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.320853</v>
+        <v>0.173592</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.225937</v>
+        <v>0.299616</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7566,10 +7566,10 @@
         <v>0.00656</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.604085</v>
+        <v>0.458381</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.335563</v>
+        <v>0.350753</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7652,10 +7652,10 @@
         <v>0.000766</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.581863</v>
+        <v>0.481436</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.265921</v>
+        <v>0.19278</v>
       </c>
       <c r="H169" t="n">
         <v>1</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.266769</v>
+        <v>0.205397</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.260181</v>
+        <v>0.25974</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.414</v>
+        <v>0.360904</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.234084</v>
+        <v>0.150233</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.228489</v>
+        <v>0.202715</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.194936</v>
+        <v>0.126004</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7996,10 +7996,10 @@
         <v>0.002133</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.603343</v>
+        <v>0.439624</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.187995</v>
+        <v>0.116139</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.190376</v>
+        <v>0.192422</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.139837</v>
+        <v>0.212996</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.084172</v>
+        <v>0.102177</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>0.69765</v>
+        <v>0.7231610000000001</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.29067</v>
+        <v>0.355747</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.122196</v>
+        <v>0.16077</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.233528</v>
+        <v>0.226222</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.182631</v>
+        <v>0.198225</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.199098</v>
+        <v>0.253027</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.27513</v>
+        <v>0.271713</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.15511</v>
+        <v>0.131191</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.252321</v>
+        <v>0.265404</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.856612</v>
+        <v>0.75309</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.526805</v>
+        <v>0.540744</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>0.51513</v>
+        <v>0.60784</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.589483</v>
+        <v>0.522078</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.336316</v>
+        <v>0.278081</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.257687</v>
+        <v>0.450759</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="G196" t="n">
-        <v>0.776716</v>
+        <v>0.841028</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.950746</v>
+        <v>0.937732</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.924766</v>
+        <v>0.921892</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>0.378059</v>
+        <v>0.365967</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.290191</v>
+        <v>0.236408</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.255781</v>
+        <v>0.255685</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.156325</v>
+        <v>0.132113</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.37462</v>
+        <v>0.292541</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.449265</v>
+        <v>0.361296</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.111799</v>
+        <v>0.109899</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.666463</v>
+        <v>0.7952399999999999</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0.586318</v>
+        <v>0.771863</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.265951</v>
+        <v>0.225592</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9415,10 +9415,10 @@
         <v>9.6e-05</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.5047779999999999</v>
+        <v>0.288828</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.683917</v>
+        <v>0.648954</v>
       </c>
       <c r="H210" t="n">
         <v>1</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.09850100000000001</v>
+        <v>0.07591199999999999</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.188786</v>
+        <v>0.118594</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9587,10 +9587,10 @@
         <v>0.001989</v>
       </c>
       <c r="F213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.543504</v>
+        <v>0.331382</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.369915</v>
+        <v>0.251585</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.228489</v>
+        <v>0.116202</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.482201</v>
+        <v>0.358382</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.052144</v>
+        <v>0.040846</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>0.65685</v>
+        <v>0.575692</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="G219" t="n">
-        <v>0.689874</v>
+        <v>0.621484</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.147289</v>
+        <v>0.109447</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.275832</v>
+        <v>0.237598</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.55332</v>
+        <v>0.608797</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.198682</v>
+        <v>0.150717</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.306798</v>
+        <v>0.232634</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10103,10 +10103,10 @@
         <v>0.725016</v>
       </c>
       <c r="F225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0.471112</v>
+        <v>0.5141210000000001</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.363785</v>
+        <v>0.387298</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10189,10 +10189,10 @@
         <v>0.029652</v>
       </c>
       <c r="F227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.519817</v>
+        <v>0.431802</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.423822</v>
+        <v>0.290572</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.09110699999999999</v>
+        <v>0.061474</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.1295</v>
+        <v>0.141073</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10361,10 +10361,10 @@
         <v>0.988102</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.495845</v>
+        <v>0.618409</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.307807</v>
+        <v>0.269953</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0.29329</v>
+        <v>0.334313</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.344113</v>
+        <v>0.364203</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.918685</v>
+        <v>0.958829</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.20381</v>
+        <v>0.176362</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.198223</v>
+        <v>0.087908</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.269632</v>
+        <v>0.171798</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.13511</v>
+        <v>0.078316</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.155185</v>
+        <v>0.147615</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.282054</v>
+        <v>0.158476</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.143333</v>
+        <v>0.09773999999999999</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.472072</v>
+        <v>0.340405</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.40366</v>
+        <v>0.332903</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10963,10 +10963,10 @@
         <v>9e-06</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0.544238</v>
+        <v>0.390601</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.718899</v>
+        <v>0.891226</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.963517</v>
+        <v>0.990967</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.707501</v>
+        <v>0.879741</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.9605900000000001</v>
+        <v>0.989883</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.290301</v>
+        <v>0.217858</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.278675</v>
+        <v>0.169358</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>0.469974</v>
+        <v>0.373008</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.240479</v>
+        <v>0.183202</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.289553</v>
+        <v>0.291354</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.439378</v>
+        <v>0.39319</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11436,10 +11436,10 @@
         <v>0.137098</v>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>0.567971</v>
+        <v>0.459284</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.985494</v>
+        <v>0.993569</v>
       </c>
       <c r="H257" t="n">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.890439</v>
+        <v>0.87188</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>0.379962</v>
+        <v>0.312645</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.199607</v>
+        <v>0.157649</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.9009470000000001</v>
+        <v>0.922451</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.401765</v>
+        <v>0.340747</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.401518</v>
+        <v>0.367402</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.889556</v>
+        <v>0.9175990000000001</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.363906</v>
+        <v>0.339309</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.150781</v>
+        <v>0.105147</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.838414</v>
+        <v>0.819994</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.727583</v>
+        <v>0.810275</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.304112</v>
+        <v>0.208027</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.235222</v>
+        <v>0.171607</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.17974</v>
+        <v>0.099872</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12124,10 +12124,10 @@
         <v>0.002348</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>0.355636</v>
+        <v>0.543367</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0.302056</v>
+        <v>0.396601</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.545259</v>
+        <v>0.637113</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.36462</v>
+        <v>0.233649</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>0.354652</v>
+        <v>0.34866</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.23897</v>
+        <v>0.191827</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.385979</v>
+        <v>0.293533</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.282295</v>
+        <v>0.267559</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.232936</v>
+        <v>0.223812</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.14799</v>
+        <v>0.127696</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.121982</v>
+        <v>0.121579</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.27506</v>
+        <v>0.288922</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.33068</v>
+        <v>0.273372</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.328601</v>
+        <v>0.314348</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.355844</v>
+        <v>0.317635</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.716354</v>
+        <v>0.852641</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.485898</v>
+        <v>0.418784</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.321346</v>
+        <v>0.240532</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.197077</v>
+        <v>0.158168</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.374171</v>
+        <v>0.408067</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.384573</v>
+        <v>0.293476</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.359604</v>
+        <v>0.236104</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.139326</v>
+        <v>0.09107700000000001</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.284562</v>
+        <v>0.249136</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.999771</v>
+        <v>0.999945</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0.577358</v>
+        <v>0.611967</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.227542</v>
+        <v>0.268465</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0.7706</v>
+        <v>0.859559</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0.873008</v>
+        <v>0.825557</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.162026</v>
+        <v>0.217389</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.259916</v>
+        <v>0.216183</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.952559</v>
+        <v>0.978281</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.896012</v>
+        <v>0.933998</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.205036</v>
+        <v>0.184011</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.345336</v>
+        <v>0.339425</v>
       </c>
       <c r="H306" t="n">
         <v>1</v>
@@ -13629,10 +13629,10 @@
         <v>0.056228</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>0.477717</v>
+        <v>0.56443</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0.732934</v>
+        <v>0.764964</v>
       </c>
       <c r="H308" t="n">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.821087</v>
+        <v>0.829995</v>
       </c>
       <c r="H309" t="n">
         <v>1</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.269429</v>
+        <v>0.146636</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.265431</v>
+        <v>0.190657</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.136216</v>
+        <v>0.092503</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.257201</v>
+        <v>0.27312</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
